--- a/daily_matches/job_matches_2026-04-10.xlsx
+++ b/daily_matches/job_matches_2026-04-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Duetto Research</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17.8</v>
+        <v>16.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, TensorFlow, PyTorch, Docker, Kubernetes, Git, Kafka, Hadoop, NoSQL, Tableau</t>
+          <t>RAG, S3, EC2, CI/CD, Jenkins, GitHub Actions, Terraform, Git, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c3639e1ca81b020</t>
+          <t>https://www.indeed.com/viewjob?jk=dd129b5d9457ac57</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Data Engineer, Revenue Intelligence</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bechtel</t>
+          <t>GitHub</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Copilot, MLflow, Git, Databricks, Python, SQL, R</t>
+          <t>RAG, Copilot, Synapse, Docker, CI/CD, GitHub Actions, Git, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,42 +531,357 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37332ce15c26ec07</t>
+          <t>https://www.indeed.com/viewjob?jk=fbd118d6be25a868</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Applied AI ML Engineer-Senior Associate</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CLEARCO</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, Docker, Kubernetes, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3a2866cc2d33c026</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Applied AI ML-Senior Associate</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, CI/CD, Jenkins, Terraform, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0a9e6e4bfd928904</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Sr. Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Ellucian</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a5c6c22bfb3d302d</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Sr AI Security Engineer</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>7-Eleven</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Docker, Kubernetes, GitHub Actions, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=03c42902c0bf3d6c</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Senior Analyst Conversational AI Analytics</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>National Debt Relief</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
           <t>US USA</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D8" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>RAG, Git, Tableau, Power BI, Python, SQL, R, Scala, Optimization, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4e9747a7c66dbd0f</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Data Scientist - Innovation - PhD (Irving, TX)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Caris Life Sciences</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, PyTorch, S3, EC2, MLflow, Docker, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bb63e7f051e9255d</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer - Knowledge Platform</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
         <v>10</v>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, BigQuery, Snowflake, BigQuery, Python, SQL, R, Hypothesis Testing</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1980114dc669c49d</t>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>BigQuery, Snowflake, BigQuery, PostgreSQL, MySQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4a97391e031fbe7e</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Senior Engineer</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>10</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, NoSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e55e25e3c6cd3752</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Senior Engineer</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>10</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, NoSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c6b2ffe5d9c2ef14</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>AI Systems Fellow – Private Equity | Filion Capital</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>10</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Pinecone, ChromaDB, Prompt Engineering, FastAPI, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9c46e8a577a7ec4a</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-10.xlsx
+++ b/daily_matches/job_matches_2026-04-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,12 +468,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Senior Software and Integrations Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Duetto Research</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -482,33 +482,33 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16.7</v>
+        <v>18.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, CI/CD, Jenkins, GitHub Actions, Terraform, Git, MongoDB, NoSQL</t>
+          <t>LangChain, RAG, LLaMA, Data Lake, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd129b5d9457ac57</t>
+          <t>https://www.indeed.com/viewjob?jk=be70c6be9df15447</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Revenue Intelligence</t>
+          <t>2-6 Month Senior Data Engineer Contract</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>GitHub</t>
+          <t>Tripledot Studios</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -517,46 +517,46 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14.4</v>
+        <v>17.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Synapse, Docker, CI/CD, GitHub Actions, Git, Power BI, Python, SQL</t>
+          <t>AI Engineer, Data Scientist, Generative AI, Redshift, Data Lake, Docker, Kubernetes, CI/CD, Git, Redshift</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbd118d6be25a868</t>
+          <t>https://www.indeed.com/viewjob?jk=1492e3665cbc949b</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Applied AI ML Engineer-Senior Associate</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>12.2</v>
+        <v>17.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, Docker, Kubernetes, Python, R, Scala</t>
+          <t>RAG, S3, Docker, Kubernetes, Apache Airflow, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a2866cc2d33c026</t>
+          <t>https://www.indeed.com/viewjob?jk=a49b45df7b2ac405</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Applied AI ML-Senior Associate</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Tripledot Studios</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, CI/CD, Jenkins, Terraform, Git, Python, R, Java</t>
+          <t>Machine Learning Engineer, Generative AI, Copilot, MLflow, Docker, Kubernetes, CI/CD, Git, Matplotlib, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,67 +601,67 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a9e6e4bfd928904</t>
+          <t>https://www.indeed.com/viewjob?jk=425bac685c7d6d02</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sr. Cloud Engineer</t>
+          <t>Multi-Cloud SQL/Oracle Database Administrator (DBA)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ellucian</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, SQL, R, Scala</t>
+          <t>RAG, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Kafka, PostgreSQL, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5c6c22bfb3d302d</t>
+          <t>https://www.indeed.com/viewjob?jk=7518086fa359e2be</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sr AI Security Engineer</t>
+          <t>Data Scientist I</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>7-Eleven</t>
+          <t>Webster University</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, Machine Learning Engineer, RAG, Docker, Kubernetes, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Docker, Hadoop, Tableau, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,67 +671,67 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03c42902c0bf3d6c</t>
+          <t>https://www.indeed.com/viewjob?jk=bd21adcbb6f4fbac</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Analyst Conversational AI Analytics</t>
+          <t>Data Scientist I</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>National Debt Relief</t>
+          <t>Convey Health Solutions</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Git, Tableau, Power BI, Python, SQL, R, Scala, Optimization, A/B Testing</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Docker, Hadoop, Tableau, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e9747a7c66dbd0f</t>
+          <t>https://www.indeed.com/viewjob?jk=a6c7cbfa1f1ffb22</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Scientist - Innovation - PhD (Irving, TX)</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Caris Life Sciences</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>HI, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, PyTorch, S3, EC2, MLflow, Docker, Git, Python, R</t>
+          <t>Generative AI, RAG, Copilot, CI/CD, Jenkins, Git, Kafka, PostgreSQL, SQL, R</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb63e7f051e9255d</t>
+          <t>https://www.indeed.com/viewjob?jk=61859efe066d7fac</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Knowledge Platform</t>
+          <t>Systems Integration</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Airwallex</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>BigQuery, Snowflake, BigQuery, PostgreSQL, MySQL, Python, SQL, R, Scala</t>
+          <t>RAG, Cortex, Synapse, Git, Snowflake, Databricks, PySpark, Kafka, Python, SQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,112 +776,287 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a97391e031fbe7e</t>
+          <t>https://www.indeed.com/viewjob?jk=ee3e5429ee3772bd</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Senior Associate, Data Scientist</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, NoSQL, Python, SQL, R, Java, Scala</t>
+          <t>Data Scientist, LangChain, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Snowflake, Python, SQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e55e25e3c6cd3752</t>
+          <t>https://www.indeed.com/viewjob?jk=224ead127502bc58</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Senior Java Full Stack Engineer (w/Angular 16+) - Onsite Hybrid</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Smithfield, RI, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, NoSQL, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, R, Java, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6b2ffe5d9c2ef14</t>
+          <t>https://www.indeed.com/viewjob?jk=5c8b6c5379540fd4</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AI Systems Fellow – Private Equity | Filion Capital</t>
+          <t>Senior Java Full Stack Engineer (w/Angular 16+) - Onsite Hybrid</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cf90fab769614217</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Dell Technologies</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Round Rock, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
         <v>10</v>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>LangChain, RAG, Pinecone, ChromaDB, Prompt Engineering, FastAPI, Git, Python, R</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Docker, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
         <is>
           <t>2026-04-10</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9c46e8a577a7ec4a</t>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=962f4ecd6d0b23ef</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>10</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d1c0551e51d2fda9</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Data Scientist (PHD Required)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Magnite</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>10</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, AKS, Hadoop, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b00262d8acd361bd</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence (AI) Intern</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>CRDF Global</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Arlington, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>10</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, Copilot, Git, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1b43b61ed056385f</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Sr. Data Analyst-Xumo</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Comcast</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Irvine, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>10</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>BigQuery, Git, BigQuery, Hadoop, SQL, R, Optimization, Hypothesis Testing, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5ab26beda1e73349</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-10.xlsx
+++ b/daily_matches/job_matches_2026-04-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sr. Data Analyst, Medical Analytics (Remote)</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Sorcero</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>12.2</v>
+        <v>17.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Redshift, BigQuery, Snowflake, BigQuery, Redshift, Tableau, Power BI, Python, SQL, R</t>
+          <t>RAG, S3, Docker, Kubernetes, Apache Airflow, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,42 +496,602 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a859f3d984cde7ec</t>
+          <t>https://www.indeed.com/viewjob?jk=075c352d5919b190</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Strategist</t>
+          <t>Senior Associate - Sr. Quality Test Engineer (SDET)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Greenville-Spartanburg International Airport</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Greer, SC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, MySQL, NoSQL</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=874459add6faf56d</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Beehyv</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>McKinney, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, Terraform, Git, Snowflake, Databricks, PySpark, Power BI, Python</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=28fc8ff707127a1b</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Azure + AWS Cloud Engineer (GPT Model Integration, Prompt Engineering)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>S R International Inc</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Harrisburg, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, S3, EC2, Docker, Kubernetes, AKS, CI/CD, Git, Python</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ecffc87de58c4bef</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>AI COE Analyst</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Foster City, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Data Scientist, LangChain, LLaMA, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, CI/CD, Databricks, Kafka</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=63dabaf19b3734a8</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>American business solutions inc</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Harrisburg, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, S3, EC2, Docker, Kubernetes, AKS, CI/CD, Git, Python</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cc38211228fd0f17</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>AI Integration Engineer (Java + AI)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>RAG, S3, Docker, Kubernetes, CI/CD, Git, Kafka, NoSQL, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9a0a23fabb87369f</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>AI Integration Engineer (Java + AI)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>HI, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Copilot, CI/CD, Jenkins, Git, Kafka, PostgreSQL, SQL, R</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f7bd5de39a297655</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Data Surge</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>FastAPI, Docker, Kubernetes, CI/CD, Databricks, MySQL, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=831b9a194e58c913</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>RAG, Data Lake, Kinesis, Docker, Kubernetes, Terraform, Git, Kafka, Python, R</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=09cd4db2f9c6e6e1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Data Platform</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Coinbase</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, Copilot, Data Lake, Kafka, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6abe95e0e290b9c2</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>AI/ML Solutions Analyst</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>VieMed, LLC</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Lafayette, LA, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>LangChain, Copilot, Prompt Engineering, Git, Tableau, Power BI, Matplotlib, Seaborn, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=815304123b72d21c</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>AI Research Engineer</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Hex Technologies</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Copilot, Kubernetes, CI/CD, Terraform, Snowflake, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c1a01863f643fa66</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Software Engineer, Fullstack</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Hex Technologies</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Kubernetes, CI/CD, Terraform, Snowflake, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4477f31d5223f875</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Guidewire API Developer</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
         <v>10</v>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>RAG, Redshift, Synapse, Data Lake, Snowflake, Redshift, Power BI, R, Scala</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bd859599928d7193</t>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, MongoDB, Python, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e35679db31226058</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Software Enginner</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Great Neck, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>10</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Optimization</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=75ead41f5108aaef</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Data Architect - Paid Relocation to Cincinnati</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Total Quality Logistics (TQL)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Cincinnati, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>10</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>RAG, Synapse, Databricks, Kafka, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c40e1674aa706aac</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Software Engineer - Development and Product Support (On-site-Hybrid 3 days in Alpharetta or Atlanta, Georgia Only)</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Global Payments</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Alpharetta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>10</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>TensorFlow, Hadoop, MySQL, NoSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=976a75f332680b22</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-10.xlsx
+++ b/daily_matches/job_matches_2026-04-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>DevOps Engineer (AI/ML)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Global Payments</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Columbus, GA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17.8</v>
+        <v>23.3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, S3, Docker, Kubernetes, Apache Airflow, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
+          <t>Data Scientist, LangChain, RAG, Copilot, Pinecone, Prompt Engineering, GCP Vertex AI, Azure ML, MLflow, Docker</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,67 +496,67 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=075c352d5919b190</t>
+          <t>https://www.indeed.com/viewjob?jk=c0583eb15ac45170</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Associate - Sr. Quality Test Engineer (SDET)</t>
+          <t>DevOps Engineer (AI/ML)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>Global Payments</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.8</v>
+        <v>23.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, MySQL, NoSQL</t>
+          <t>Data Scientist, LangChain, RAG, Copilot, Pinecone, Prompt Engineering, GCP Vertex AI, Azure ML, MLflow, Docker</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=874459add6faf56d</t>
+          <t>https://www.indeed.com/viewjob?jk=58e0b50be31f6904</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior DataOps Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Beehyv</t>
+          <t>Smile Digital Health</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>McKinney, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>14.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Terraform, Git, Snowflake, Databricks, PySpark, Power BI, Python</t>
+          <t>RAG, Kubernetes, Apache Airflow, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Databricks, Python</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28fc8ff707127a1b</t>
+          <t>https://www.indeed.com/viewjob?jk=a43d8e0d307a2b20</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Azure + AWS Cloud Engineer (GPT Model Integration, Prompt Engineering)</t>
+          <t>AI Support Engineer (II+)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>S R International Inc</t>
+          <t>Global Payments</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, S3, EC2, Docker, Kubernetes, AKS, CI/CD, Git, Python</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Prompt Engineering, Cortex, GCP Vertex AI, CI/CD, Snowflake, Kafka</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecffc87de58c4bef</t>
+          <t>https://www.indeed.com/viewjob?jk=480fc48b094aaac8</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AI COE Analyst</t>
+          <t>AI Support Engineer (II+)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Global Payments</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Columbus, GA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, LLaMA, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, CI/CD, Databricks, Kafka</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Prompt Engineering, Cortex, GCP Vertex AI, CI/CD, Snowflake, Kafka</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63dabaf19b3734a8</t>
+          <t>https://www.indeed.com/viewjob?jk=456b8596f0d88ee9</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>American business solutions inc</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, S3, EC2, Docker, Kubernetes, AKS, CI/CD, Git, Python</t>
+          <t>RAG, TensorFlow, PyTorch, Keras, spaCy, Azure ML, Azure ML Studio, FastAPI, Kubernetes, Terraform</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc38211228fd0f17</t>
+          <t>https://www.indeed.com/viewjob?jk=9ec04fe2a39313ff</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Associate Software Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, S3, Docker, Kubernetes, CI/CD, Git, Kafka, NoSQL, Python, SQL</t>
+          <t>RAG, Copilot, AKS, CI/CD, GitHub Actions, Terraform, Git, Tableau, Python, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a0a23fabb87369f</t>
+          <t>https://www.indeed.com/viewjob?jk=d5638c393c38c555</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>My Desk</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>HI, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, CI/CD, Jenkins, Git, Kafka, PostgreSQL, SQL, R</t>
+          <t>Generative AI, RAG, S3, EC2, Docker, Kubernetes, CI/CD, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7bd5de39a297655</t>
+          <t>https://www.indeed.com/viewjob?jk=d58c8737e52387b9</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Sr. Full Stack Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Data Surge</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>FastAPI, Docker, Kubernetes, CI/CD, Databricks, MySQL, NoSQL, Python, SQL, R</t>
+          <t>RAG, Copilot, CI/CD, Jenkins, Git, Kafka, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=831b9a194e58c913</t>
+          <t>https://www.indeed.com/viewjob?jk=77f3f1a9fe5bd877</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer 4 - (Java Developer) (AI‑Enabled Development)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tech Interacts Inc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, Kinesis, Docker, Kubernetes, Terraform, Git, Kafka, Python, R</t>
+          <t>RAG, Copilot, CI/CD, Jenkins, Git, MySQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09cd4db2f9c6e6e1</t>
+          <t>https://www.indeed.com/viewjob?jk=4a7b99f154f63c3f</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Data Platform</t>
+          <t>Specialist Data Engineering</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Coinbase</t>
+          <t>Rio Tinto</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Copilot, Data Lake, Kafka, Python, SQL, R, Java</t>
+          <t>Data Scientist, RAG, CI/CD, Git, Databricks, PySpark, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,59 +846,59 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6abe95e0e290b9c2</t>
+          <t>https://www.indeed.com/viewjob?jk=12141d827aef2872</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AI/ML Solutions Analyst</t>
+          <t>Pentaho BI SME</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>VieMed, LLC</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Lafayette, LA, US USA</t>
+          <t>San Juan, PR, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>LangChain, Copilot, Prompt Engineering, Git, Tableau, Power BI, Matplotlib, Seaborn, Python, SQL</t>
+          <t>RAG, S3, Git, Hadoop, PostgreSQL, MySQL, NoSQL, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=815304123b72d21c</t>
+          <t>https://www.indeed.com/viewjob?jk=565631a2f4f36e37</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AI Research Engineer</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Hex Technologies</t>
+          <t>Chess.com</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Copilot, Kubernetes, CI/CD, Terraform, Snowflake, Python, SQL, R</t>
+          <t>RAG, Kubernetes, Terraform, MySQL, Cassandra, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1a01863f643fa66</t>
+          <t>https://www.indeed.com/viewjob?jk=dbfa35adc5a9ae23</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Engineer, Fullstack</t>
+          <t>Jr Backend Software Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Hex Technologies</t>
+          <t>YouDecide</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Glen Allen, VA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Kubernetes, CI/CD, Terraform, Snowflake, Python, SQL, R, Scala</t>
+          <t>RAG, Docker, CI/CD, Jenkins, GitHub Actions, Git, SQL, R, Java</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4477f31d5223f875</t>
+          <t>https://www.indeed.com/viewjob?jk=74f3e545688e9b28</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Guidewire API Developer</t>
+          <t>AI Search Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, MongoDB, Python, SQL, R, Java, Scala, Optimization</t>
+          <t>FastAPI, Docker, Kubernetes, AKS, CI/CD, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e35679db31226058</t>
+          <t>https://www.indeed.com/viewjob?jk=e1b361235c74598d</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Enginner</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Core &amp; Main</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Great Neck, NY, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Optimization</t>
+          <t>RAG, Data Lake, CI/CD, Databricks, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,77 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75ead41f5108aaef</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Data Architect - Paid Relocation to Cincinnati</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Total Quality Logistics (TQL)</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Cincinnati, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>10</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>RAG, Synapse, Databricks, Kafka, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c40e1674aa706aac</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Software Engineer - Development and Product Support (On-site-Hybrid 3 days in Alpharetta or Atlanta, Georgia Only)</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Global Payments</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Alpharetta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>10</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>TensorFlow, Hadoop, MySQL, NoSQL, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=976a75f332680b22</t>
+          <t>https://www.indeed.com/viewjob?jk=57136340cc4fdeeb</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-10.xlsx
+++ b/daily_matches/job_matches_2026-04-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,87 +468,87 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>DevOps Engineer (AI/ML)</t>
+          <t>Senior Analytics Engineer 2026 - US,UK</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>Aimpoint Digital</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Columbus, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>23.3</v>
+        <v>21.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, Copilot, Pinecone, Prompt Engineering, GCP Vertex AI, Azure ML, MLflow, Docker</t>
+          <t>Data Scientist, RAG, Copilot, Cortex, Redshift, BigQuery, Synapse, CI/CD, Git, Snowflake</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0583eb15ac45170</t>
+          <t>https://www.indeed.com/viewjob?jk=03a74124134b4635</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DevOps Engineer (AI/ML)</t>
+          <t>Senior AI/ML Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>GESTURE</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>23.3</v>
+        <v>17.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, Copilot, Pinecone, Prompt Engineering, GCP Vertex AI, Azure ML, MLflow, Docker</t>
+          <t>RAG, Pinecone, TensorFlow, PyTorch, XGBoost, BigQuery, Dataflow, AKS, Git, BigQuery</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58e0b50be31f6904</t>
+          <t>https://www.indeed.com/viewjob?jk=8166abc50850e8cd</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior DataOps Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Smile Digital Health</t>
+          <t>Authenticx</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, Apache Airflow, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Databricks, Python</t>
+          <t>Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, spaCy, Docker, Kubernetes, Matplotlib, Python, SQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a43d8e0d307a2b20</t>
+          <t>https://www.indeed.com/viewjob?jk=ee81ead1143fec4d</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI Support Engineer (II+)</t>
+          <t>ML Infrastructure/Platform Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Prompt Engineering, Cortex, GCP Vertex AI, CI/CD, Snowflake, Kafka</t>
+          <t>Data Scientist, LangChain, RAG, MLflow, Docker, Kubernetes, CI/CD, Git, Snowflake, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=480fc48b094aaac8</t>
+          <t>https://www.indeed.com/viewjob?jk=4fee9a8a881ab20d</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AI Support Engineer (II+)</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>BakerHostetler</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Columbus, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Prompt Engineering, Cortex, GCP Vertex AI, CI/CD, Snowflake, Kafka</t>
+          <t>RAG, S3, Data Lake, CI/CD, GitHub Actions, Git, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=456b8596f0d88ee9</t>
+          <t>https://www.indeed.com/viewjob?jk=8c94745964a1903b</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Asset &amp; Wealth Management - Software Engineer - Associate - Dallas</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, Keras, spaCy, Azure ML, Azure ML Studio, FastAPI, Kubernetes, Terraform</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka, MongoDB, SQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ec04fe2a39313ff</t>
+          <t>https://www.indeed.com/viewjob?jk=363a81b7a4ffa5a8</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Associate Software Engineer</t>
+          <t>Full Stack Developer – AI Projects</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>General Property Construction</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Doral, FL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Copilot, AKS, CI/CD, GitHub Actions, Terraform, Git, Tableau, Python, R</t>
+          <t>Docker, Kubernetes, CI/CD, Git, PostgreSQL, MySQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5638c393c38c555</t>
+          <t>https://www.indeed.com/viewjob?jk=736e7d6f95444207</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Software Engineer, Growth</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>My Desk</t>
+          <t>Klaviyo</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, S3, EC2, Docker, Kubernetes, CI/CD, Terraform, Git, Python</t>
+          <t>RAG, EC2, Terraform, Git, MySQL, Cassandra, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d58c8737e52387b9</t>
+          <t>https://www.indeed.com/viewjob?jk=e52c85b2cb6e195c</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sr. Full Stack Engineer</t>
+          <t>Sr. Machine Learning Engineer (MLE)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Equinix</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Jenkins, Git, Kafka, Python, R, Java, Scala</t>
+          <t>Machine Learning Engineer, Generative AI, RAG, TensorFlow, PyTorch, Git, Kafka, Hadoop, Python, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77f3f1a9fe5bd877</t>
+          <t>https://www.indeed.com/viewjob?jk=6d9b4fa02a5a7631</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software Engineer 4 - (Java Developer) (AI‑Enabled Development)</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Tech Interacts Inc</t>
+          <t>C4ADS</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Jenkins, Git, MySQL, Python, SQL, R, Java</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Pinecone, Prompt Engineering, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a7b99f154f63c3f</t>
+          <t>https://www.indeed.com/viewjob?jk=305f1b6f9f64804f</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Specialist Data Engineering</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Rio Tinto</t>
+          <t>Loenbro</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Centennial, CO, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, CI/CD, Git, Databricks, PySpark, Python, SQL, R, Scala</t>
+          <t>RAG, Dataflow, CI/CD, Git, Snowflake, PySpark, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12141d827aef2872</t>
+          <t>https://www.indeed.com/viewjob?jk=d3bce0d5c31544a7</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Pentaho BI SME</t>
+          <t>Sr. Data Engineer I</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>DoubleVerify</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>San Juan, PR, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,34 +871,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, S3, Git, Hadoop, PostgreSQL, MySQL, NoSQL, SQL, R, Optimization</t>
+          <t>RAG, Docker, CI/CD, Git, Python, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=565631a2f4f36e37</t>
+          <t>https://www.indeed.com/viewjob?jk=383affd6063bd3a2</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>Data Scientist I - Advanced Analytics</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Chess.com</t>
+          <t>Novo Nordisk, Inc.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plainsboro, NJ, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, Terraform, MySQL, Cassandra, Python, SQL, R, Scala, Optimization</t>
+          <t>Data Scientist, RAG, CI/CD, Git, Snowflake, Tableau, Python, SQL, R, A/B Testing</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbfa35adc5a9ae23</t>
+          <t>https://www.indeed.com/viewjob?jk=2b6869c39d84dd55</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Jr Backend Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>YouDecide</t>
+          <t>Pansophic Learning</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Glen Allen, VA, US USA</t>
+          <t>Tysons, VA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Docker, CI/CD, Jenkins, GitHub Actions, Git, SQL, R, Java</t>
+          <t>S3, EC2, Redshift, Git, Redshift, MongoDB, NoSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74f3e545688e9b28</t>
+          <t>https://www.indeed.com/viewjob?jk=f1e2ece52e0765ad</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AI Search Engineer</t>
+          <t>Software Engineer IV</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Trinity Health - IHA</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>FastAPI, Docker, Kubernetes, AKS, CI/CD, Git, Python, R, Scala</t>
+          <t>Copilot, CI/CD, Git, Python, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1b361235c74598d</t>
+          <t>https://www.indeed.com/viewjob?jk=cab012d353c00005</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Software Engineer, AI Infrastructure</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Core &amp; Main</t>
+          <t>Robinhood</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Menlo Park, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, CI/CD, Databricks, Power BI, Python, SQL, R, Scala</t>
+          <t>Data Scientist, Generative AI, RAG, ChromaDB, TensorFlow, PyTorch, Python, R, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,7 +1021,252 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57136340cc4fdeeb</t>
+          <t>https://www.indeed.com/viewjob?jk=bc2e6f5fe8613280</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Software Engineer, Gemini App, Info Seek, Quality, DeepMind</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>DeepMind</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Mountain View, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>10</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>RAG, Gemini, Prompt Engineering, TensorFlow, PyTorch, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0d37571316049aa4</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Sr. Quality Engineer</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Realtime Clinical Trial Management Systems</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>10</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8b4fd87ec67baab1</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Site Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Equifax</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Alpharetta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>10</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7511c9c5af76f3d8</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Senior AI Software Engineer</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Dearborn, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>10</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, TensorFlow, PyTorch, XGBoost, LightGBM, Python, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ef0c721d33e73062</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>TechnoMile</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>10</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, CI/CD, Jenkins, Terraform, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ddfa44160a2bd5aa</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>ISHIR</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>10</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fa224911a96672a0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Doppel Farmaceutici</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, BigQuery, Git, BigQuery, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=589e804a5bbbcd32</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-10.xlsx
+++ b/daily_matches/job_matches_2026-04-10.xlsx
@@ -468,95 +468,95 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer 2026 - US,UK</t>
+          <t>Guidewire API Developer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Aimpoint Digital</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>21.1</v>
+        <v>18.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Copilot, Cortex, Redshift, BigQuery, Synapse, CI/CD, Git, Snowflake</t>
+          <t>Copilot, S3, EC2, Redshift, Docker, Kubernetes, Apache Airflow, CI/CD, Jenkins, Git</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03a74124134b4635</t>
+          <t>https://www.indeed.com/viewjob?jk=29ed04d19483441d</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer</t>
+          <t>Senior Data Engineer, Global</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>GESTURE</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.8</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Pinecone, TensorFlow, PyTorch, XGBoost, BigQuery, Dataflow, AKS, Git, BigQuery</t>
+          <t>Data Scientist, RAG, Synapse, Data Lake, CI/CD, Git, Snowflake, Databricks, PostgreSQL, Power BI</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8166abc50850e8cd</t>
+          <t>https://www.indeed.com/viewjob?jk=99dcb67444244ecd</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Data Engineer, Global</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Authenticx</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, spaCy, Docker, Kubernetes, Matplotlib, Python, SQL</t>
+          <t>Data Scientist, RAG, Synapse, Data Lake, CI/CD, Git, Snowflake, Databricks, PostgreSQL, Power BI</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee81ead1143fec4d</t>
+          <t>https://www.indeed.com/viewjob?jk=cc7cabf779bdafae</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ML Infrastructure/Platform Engineer</t>
+          <t>Guidewire API Developer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, MLflow, Docker, Kubernetes, CI/CD, Git, Snowflake, Python</t>
+          <t>Generative AI, RAG, Docker, Kubernetes, Jenkins, Git, Kafka, MongoDB, NoSQL, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fee9a8a881ab20d</t>
+          <t>https://www.indeed.com/viewjob?jk=12c7db9666c539fb</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BakerHostetler</t>
+          <t>Uber</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, S3, Data Lake, CI/CD, GitHub Actions, Git, PostgreSQL, Python, SQL, R</t>
+          <t>RAG, S3, Redshift, BigQuery, Apache Airflow, BigQuery, Redshift, Kafka, Hadoop, Python</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c94745964a1903b</t>
+          <t>https://www.indeed.com/viewjob?jk=f86a75694dac8d84</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Asset &amp; Wealth Management - Software Engineer - Associate - Dallas</t>
+          <t>AI Engineer-2</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,42 +661,42 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka, MongoDB, SQL</t>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, NoSQL, SQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=363a81b7a4ffa5a8</t>
+          <t>https://www.indeed.com/viewjob?jk=299d8e30256b9fcf</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Full Stack Developer – AI Projects</t>
+          <t>Software Engineer - CRM Engineering</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>General Property Construction</t>
+          <t>Electronic Arts</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Doral, FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Git, PostgreSQL, MySQL, Python, SQL, R, Java</t>
+          <t>Generative AI, LangChain, RAG, Prompt Engineering, CI/CD, NoSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=736e7d6f95444207</t>
+          <t>https://www.indeed.com/viewjob?jk=2b287a67810a1b00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Growth</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Klaviyo</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, EC2, Terraform, Git, MySQL, Cassandra, Python, SQL, R, Java</t>
+          <t>Copilot, CI/CD, Git, Snowflake, Databricks, PySpark, MySQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e52c85b2cb6e195c</t>
+          <t>https://www.indeed.com/viewjob?jk=17b5c5a8dea42109</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sr. Machine Learning Engineer (MLE)</t>
+          <t>Guidewire API Developer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Equinix</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, RAG, TensorFlow, PyTorch, Git, Kafka, Hadoop, Python, R</t>
+          <t>RAG, Copilot, Prompt Engineering, CI/CD, NoSQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d9b4fa02a5a7631</t>
+          <t>https://www.indeed.com/viewjob?jk=136cc27686024664</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Sr. AI Developer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>C4ADS</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,34 +801,34 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Pinecone, Prompt Engineering, Git, Python, SQL</t>
+          <t>AI Engineer, RAG, Prompt Engineering, TensorFlow, PyTorch, CI/CD, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=305f1b6f9f64804f</t>
+          <t>https://www.indeed.com/viewjob?jk=dfb0b8ba243e5424</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Software Engineer, Member AI Features</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Loenbro</t>
+          <t>SoFi</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Centennial, CO, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Dataflow, CI/CD, Git, Snowflake, PySpark, Python, SQL, R, Scala</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, PostgreSQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3bce0d5c31544a7</t>
+          <t>https://www.indeed.com/viewjob?jk=f957656496074d01</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer I</t>
+          <t>Cloud AI Consultant</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>DoubleVerify</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Docker, CI/CD, Git, Python, SQL, R, Java, Scala, Optimization</t>
+          <t>Data Scientist, TensorFlow, PyTorch, XGBoost, Docker, Kubernetes, CI/CD, Python, R, Optimization</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=383affd6063bd3a2</t>
+          <t>https://www.indeed.com/viewjob?jk=b0f9363aef83a52e</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Scientist I - Advanced Analytics</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Novo Nordisk, Inc.</t>
+          <t>Route</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Plainsboro, NJ, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, CI/CD, Git, Snowflake, Tableau, Python, SQL, R, A/B Testing</t>
+          <t>RAG, S3, Terraform, Snowflake, Databricks, Tableau, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b6869c39d84dd55</t>
+          <t>https://www.indeed.com/viewjob?jk=e06fc0c98a8ef702</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AI &amp; Data Analytics Architect</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Pansophic Learning</t>
+          <t>TTX</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tysons, VA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>S3, EC2, Redshift, Git, Redshift, MongoDB, NoSQL, SQL, R, Java</t>
+          <t>Generative AI, RAG, Copilot, Synapse, Data Lake, Git, Power BI, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1e2ece52e0765ad</t>
+          <t>https://www.indeed.com/viewjob?jk=7d7156d0e2fa6911</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineer IV</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Trinity Health - IHA</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Copilot, CI/CD, Git, Python, SQL, R, Java, Scala, Optimization</t>
+          <t>Data Scientist, RAG, Redshift, Redshift, PostgreSQL, NoSQL, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cab012d353c00005</t>
+          <t>https://www.indeed.com/viewjob?jk=e1c58f7df732b9cd</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, AI Infrastructure</t>
+          <t>Senior Product Associate-Data Platform</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Robinhood</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Menlo Park, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, ChromaDB, TensorFlow, PyTorch, Python, R, Scala</t>
+          <t>Generative AI, RAG, S3, Data Lake, Git, Snowflake, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc2e6f5fe8613280</t>
+          <t>https://www.indeed.com/viewjob?jk=56230f313c3e4f90</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Software Engineer, Gemini App, Info Seek, Quality, DeepMind</t>
+          <t>AI &amp; Automation Solution Architect | Full Time</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>DeepMind</t>
+          <t>Henry Ford Health</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, Gemini, Prompt Engineering, TensorFlow, PyTorch, Python, R, Scala, Optimization</t>
+          <t>AI Engineer, RAG, TensorFlow, PyTorch, Azure ML, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,59 +1056,59 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d37571316049aa4</t>
+          <t>https://www.indeed.com/viewjob?jk=01f5f37082ca6927</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr. Quality Engineer</t>
+          <t>DevOps Miami</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Realtime Clinical Trial Management Systems</t>
+          <t>Pelico</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java, Scala</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b4fd87ec67baab1</t>
+          <t>https://www.indeed.com/viewjob?jk=cadf0132866f1439</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Java AI / ML Integration Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Python, R, Java</t>
+          <t>LangChain, LLaMA, Kubernetes, CI/CD, PostgreSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7511c9c5af76f3d8</t>
+          <t>https://www.indeed.com/viewjob?jk=b110896f0ace23c0</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior AI Software Engineer</t>
+          <t>Java AI / ML Integration Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>LangChain, RAG, TensorFlow, PyTorch, XGBoost, LightGBM, Python, R, Optimization</t>
+          <t>LangChain, LLaMA, Kubernetes, CI/CD, PostgreSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef0c721d33e73062</t>
+          <t>https://www.indeed.com/viewjob?jk=20988dccfe7b4b69</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Sr AI/ML Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>TechnoMile</t>
+          <t>Vizient, Inc.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Jenkins, Terraform, Python, R, Scala, Optimization</t>
+          <t>LangChain, RAG, LLaMA, MLflow, FastAPI, CI/CD, Python, R, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddfa44160a2bd5aa</t>
+          <t>https://www.indeed.com/viewjob?jk=a592474f9146b152</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Sr. People Data Scientist</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ISHIR</t>
+          <t>SanDisk</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Milpitas, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+          <t>Data Scientist, Generative AI, RAG, Git, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa224911a96672a0</t>
+          <t>https://www.indeed.com/viewjob?jk=6ae2d9aaf806e9e9</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Java Full Stack Developer-2</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Doppel Farmaceutici</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,17 +1256,17 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, BigQuery, Git, BigQuery, Python, SQL, R, Scala</t>
+          <t>CI/CD, MongoDB, NoSQL, Python, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=589e804a5bbbcd32</t>
+          <t>https://www.indeed.com/viewjob?jk=e355e0b9865f29dd</t>
         </is>
       </c>
     </row>
